--- a/src/vocabulary_crossword_puzzles_20tabs.xlsx
+++ b/src/vocabulary_crossword_puzzles_20tabs.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kachowyau/Desktop/TechRet/Assign1/html-js-crossword/src/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kachowyau/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B87FAAE-4108-EA49-8EA9-9E191667F5CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7570F0B7-539B-EA45-A7B3-C5BB2FEE36B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15940" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15940" firstSheet="7" activeTab="19" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Puzzle_01" sheetId="1" r:id="rId1"/>
@@ -269,10 +269,10 @@
         <r>
           <rPr>
             <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="新細明體"/>
-            <family val="2"/>
-            <scheme val="minor"/>
+            <color rgb="FF000000"/>
+            <rFont val="新細明體"/>
+            <family val="1"/>
+            <charset val="136"/>
           </rPr>
           <t>6</t>
         </r>
@@ -391,10 +391,10 @@
         <r>
           <rPr>
             <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="新細明體"/>
-            <family val="2"/>
-            <scheme val="minor"/>
+            <color rgb="FF000000"/>
+            <rFont val="新細明體"/>
+            <family val="1"/>
+            <charset val="136"/>
           </rPr>
           <t>4</t>
         </r>
@@ -405,10 +405,10 @@
         <r>
           <rPr>
             <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="新細明體"/>
-            <family val="2"/>
-            <scheme val="minor"/>
+            <color rgb="FF000000"/>
+            <rFont val="新細明體"/>
+            <family val="1"/>
+            <charset val="136"/>
           </rPr>
           <t>5</t>
         </r>
@@ -419,10 +419,10 @@
         <r>
           <rPr>
             <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="新細明體"/>
-            <family val="2"/>
-            <scheme val="minor"/>
+            <color rgb="FF000000"/>
+            <rFont val="新細明體"/>
+            <family val="1"/>
+            <charset val="136"/>
           </rPr>
           <t>6</t>
         </r>
@@ -513,10 +513,10 @@
         <r>
           <rPr>
             <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="新細明體"/>
-            <family val="2"/>
-            <scheme val="minor"/>
+            <color rgb="FF000000"/>
+            <rFont val="新細明體"/>
+            <family val="1"/>
+            <charset val="136"/>
           </rPr>
           <t>2</t>
         </r>
@@ -527,10 +527,10 @@
         <r>
           <rPr>
             <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="新細明體"/>
-            <family val="2"/>
-            <scheme val="minor"/>
+            <color rgb="FF000000"/>
+            <rFont val="新細明體"/>
+            <family val="1"/>
+            <charset val="136"/>
           </rPr>
           <t>3</t>
         </r>
@@ -555,10 +555,10 @@
         <r>
           <rPr>
             <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="新細明體"/>
-            <family val="2"/>
-            <scheme val="minor"/>
+            <color rgb="FF000000"/>
+            <rFont val="新細明體"/>
+            <family val="1"/>
+            <charset val="136"/>
           </rPr>
           <t>5</t>
         </r>
@@ -649,10 +649,10 @@
         <r>
           <rPr>
             <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="新細明體"/>
-            <family val="2"/>
-            <scheme val="minor"/>
+            <color rgb="FF000000"/>
+            <rFont val="新細明體"/>
+            <family val="1"/>
+            <charset val="136"/>
           </rPr>
           <t>1</t>
         </r>
@@ -733,10 +733,10 @@
         <r>
           <rPr>
             <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="新細明體"/>
-            <family val="2"/>
-            <scheme val="minor"/>
+            <color rgb="FF000000"/>
+            <rFont val="新細明體"/>
+            <family val="1"/>
+            <charset val="136"/>
           </rPr>
           <t>7</t>
         </r>
@@ -1005,10 +1005,10 @@
         <r>
           <rPr>
             <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="新細明體"/>
-            <family val="2"/>
-            <scheme val="minor"/>
+            <color rgb="FF000000"/>
+            <rFont val="新細明體"/>
+            <family val="1"/>
+            <charset val="136"/>
           </rPr>
           <t>5</t>
         </r>
@@ -1019,10 +1019,10 @@
         <r>
           <rPr>
             <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="新細明體"/>
-            <family val="2"/>
-            <scheme val="minor"/>
+            <color rgb="FF000000"/>
+            <rFont val="新細明體"/>
+            <family val="1"/>
+            <charset val="136"/>
           </rPr>
           <t>6</t>
         </r>
@@ -1455,10 +1455,10 @@
         <r>
           <rPr>
             <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="新細明體"/>
-            <family val="2"/>
-            <scheme val="minor"/>
+            <color rgb="FF000000"/>
+            <rFont val="新細明體"/>
+            <family val="1"/>
+            <charset val="136"/>
           </rPr>
           <t>6</t>
         </r>
@@ -1755,10 +1755,10 @@
         <r>
           <rPr>
             <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="新細明體"/>
-            <family val="2"/>
-            <scheme val="minor"/>
+            <color rgb="FF000000"/>
+            <rFont val="新細明體"/>
+            <family val="1"/>
+            <charset val="136"/>
           </rPr>
           <t>8</t>
         </r>
@@ -1769,10 +1769,10 @@
         <r>
           <rPr>
             <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="新細明體"/>
-            <family val="2"/>
-            <scheme val="minor"/>
+            <color rgb="FF000000"/>
+            <rFont val="新細明體"/>
+            <family val="1"/>
+            <charset val="136"/>
           </rPr>
           <t>9</t>
         </r>
@@ -1957,10 +1957,10 @@
         <r>
           <rPr>
             <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="新細明體"/>
-            <family val="2"/>
-            <scheme val="minor"/>
+            <color rgb="FF000000"/>
+            <rFont val="新細明體"/>
+            <family val="1"/>
+            <charset val="136"/>
           </rPr>
           <t>3</t>
         </r>
@@ -2079,10 +2079,10 @@
         <r>
           <rPr>
             <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="新細明體"/>
-            <family val="2"/>
-            <scheme val="minor"/>
+            <color rgb="FF000000"/>
+            <rFont val="新細明體"/>
+            <family val="1"/>
+            <charset val="136"/>
           </rPr>
           <t>1</t>
         </r>
@@ -2191,10 +2191,10 @@
         <r>
           <rPr>
             <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="新細明體"/>
-            <family val="2"/>
-            <scheme val="minor"/>
+            <color rgb="FF000000"/>
+            <rFont val="新細明體"/>
+            <family val="1"/>
+            <charset val="136"/>
           </rPr>
           <t>9</t>
         </r>
@@ -2243,10 +2243,10 @@
         <r>
           <rPr>
             <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="新細明體"/>
-            <family val="2"/>
-            <scheme val="minor"/>
+            <color rgb="FF000000"/>
+            <rFont val="新細明體"/>
+            <family val="1"/>
+            <charset val="136"/>
           </rPr>
           <t>2</t>
         </r>
@@ -2529,10 +2529,10 @@
         <r>
           <rPr>
             <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="新細明體"/>
-            <family val="2"/>
-            <scheme val="minor"/>
+            <color rgb="FF000000"/>
+            <rFont val="新細明體"/>
+            <family val="1"/>
+            <charset val="136"/>
           </rPr>
           <t>2</t>
         </r>
@@ -2571,10 +2571,10 @@
         <r>
           <rPr>
             <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="新細明體"/>
-            <family val="2"/>
-            <scheme val="minor"/>
+            <color rgb="FF000000"/>
+            <rFont val="新細明體"/>
+            <family val="1"/>
+            <charset val="136"/>
           </rPr>
           <t>5</t>
         </r>
@@ -2585,10 +2585,10 @@
         <r>
           <rPr>
             <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="新細明體"/>
-            <family val="2"/>
-            <scheme val="minor"/>
+            <color rgb="FF000000"/>
+            <rFont val="新細明體"/>
+            <family val="1"/>
+            <charset val="136"/>
           </rPr>
           <t>6</t>
         </r>
@@ -2613,10 +2613,10 @@
         <r>
           <rPr>
             <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="新細明體"/>
-            <family val="2"/>
-            <scheme val="minor"/>
+            <color rgb="FF000000"/>
+            <rFont val="新細明體"/>
+            <family val="1"/>
+            <charset val="136"/>
           </rPr>
           <t>8</t>
         </r>
@@ -2871,10 +2871,10 @@
         <r>
           <rPr>
             <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="新細明體"/>
-            <family val="2"/>
-            <scheme val="minor"/>
+            <color rgb="FF000000"/>
+            <rFont val="新細明體"/>
+            <family val="1"/>
+            <charset val="136"/>
           </rPr>
           <t>6</t>
         </r>
@@ -2927,7 +2927,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1627" uniqueCount="225">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1627" uniqueCount="227">
   <si>
     <t>s</t>
   </si>
@@ -2992,9 +2992,6 @@
     <t>v</t>
   </si>
   <si>
-    <t>(n.) group of people</t>
-  </si>
-  <si>
     <t>n</t>
   </si>
   <si>
@@ -3022,9 +3019,6 @@
     <t>(adj./v.) finished / to finish</t>
   </si>
   <si>
-    <t>(n.) office worker</t>
-  </si>
-  <si>
     <t>(v.) to vanish</t>
   </si>
   <si>
@@ -3040,9 +3034,6 @@
     <t>(adv.) likely</t>
   </si>
   <si>
-    <t>(adj.) complete</t>
-  </si>
-  <si>
     <t>(v.) to interrupt</t>
   </si>
   <si>
@@ -3055,9 +3046,6 @@
     <t>(adj.) obvious</t>
   </si>
   <si>
-    <t>(n./v.) similar sounds</t>
-  </si>
-  <si>
     <t>(v.) to keep going</t>
   </si>
   <si>
@@ -3073,9 +3061,6 @@
     <t>(n./v.) line / to line up</t>
   </si>
   <si>
-    <t>(n.) body tissue</t>
-  </si>
-  <si>
     <t>(v./n.) to grow / growth</t>
   </si>
   <si>
@@ -3109,9 +3094,6 @@
     <t>(adj.) from another country</t>
   </si>
   <si>
-    <t>(n.) governing body</t>
-  </si>
-  <si>
     <t>(n.) how tall something is</t>
   </si>
   <si>
@@ -3127,18 +3109,12 @@
     <t>(v.) to share information</t>
   </si>
   <si>
-    <t>(v.) past of hear</t>
-  </si>
-  <si>
     <t>(v.) to provide space</t>
   </si>
   <si>
     <t>(n.) description</t>
   </si>
   <si>
-    <t>(n.) body part</t>
-  </si>
-  <si>
     <t>(n.) past events</t>
   </si>
   <si>
@@ -3244,9 +3220,6 @@
     <t>(n.) rules of language</t>
   </si>
   <si>
-    <t>(n./v.) injury / to injure</t>
-  </si>
-  <si>
     <t>(v.) to make ashamed</t>
   </si>
   <si>
@@ -3262,9 +3235,6 @@
     <t>(v.) to accomplish</t>
   </si>
   <si>
-    <t>(adj.) very bad</t>
-  </si>
-  <si>
     <t>(v.) to grow</t>
   </si>
   <si>
@@ -3286,18 +3256,12 @@
     <t>(adj.) liked by many</t>
   </si>
   <si>
-    <t>(adj.) very great</t>
-  </si>
-  <si>
     <t>(adj.) well known</t>
   </si>
   <si>
     <t>(adj.) not the same</t>
   </si>
   <si>
-    <t>(adj.) forceful</t>
-  </si>
-  <si>
     <t>(conj.) despite</t>
   </si>
   <si>
@@ -3322,9 +3286,6 @@
     <t>(n.) measurement of longness</t>
   </si>
   <si>
-    <t>(v.) to value</t>
-  </si>
-  <si>
     <t>(adj.) certain</t>
   </si>
   <si>
@@ -3535,9 +3496,6 @@
     <t>(adv.) by mistake; not on purpose</t>
   </si>
   <si>
-    <t>(n./v.) giving up</t>
-  </si>
-  <si>
     <t>(n.) communication system</t>
   </si>
   <si>
@@ -3602,6 +3560,70 @@
   </si>
   <si>
     <t>(n.) the force when you press something</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>(n.) the people living in one particular area</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>(n.) someone who works in an office, writing letters, making phone calls, etc</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>(adj.) detailed and careful</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>(n./v.) a word that has the same last sound as another word</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>(n.) body tissue that can tighten and relax to produce movement</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">(n.) a small group of people chosen to represent a larger organization </t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">(n.) the group of (usually) elected politicians </t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>(v.) past tense of hear</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>(n.) body part that join the arms to the rest of the body</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>(n./v.) an injury or mark where the skin has not been broken but is darker in colour,</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>(adj.) extremely bad or unsuccessful</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>(adj.) vvery large in amount or degree</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>(adj.) determined to win or succeed and using forceful action to do this</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>(v.) to recognize how good someone or something is and to value them or it</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>(adj.) easy to recognize</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>(n./v.) to give up something that is valuable to you in order to help another person</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -3609,7 +3631,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3635,6 +3657,13 @@
       <family val="3"/>
       <charset val="136"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="新細明體"/>
+      <family val="1"/>
+      <charset val="136"/>
     </font>
   </fonts>
   <fills count="2">
@@ -4066,7 +4095,7 @@
         <v>5</v>
       </c>
       <c r="R3" s="4" t="s">
-        <v>224</v>
+        <v>210</v>
       </c>
     </row>
     <row r="4" spans="1:18" ht="21" customHeight="1">
@@ -4117,7 +4146,7 @@
         <v>10</v>
       </c>
       <c r="R6" s="4" t="s">
-        <v>21</v>
+        <v>211</v>
       </c>
     </row>
     <row r="7" spans="1:18" ht="21" customHeight="1">
@@ -4125,7 +4154,7 @@
         <v>12</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>4</v>
@@ -4137,7 +4166,7 @@
         <v>14</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J7" s="1" t="s">
         <v>8</v>
@@ -4148,7 +4177,7 @@
         <v>12</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="9" spans="1:18" ht="21" customHeight="1">
@@ -4177,7 +4206,7 @@
         <v>17</v>
       </c>
       <c r="Q9" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="10" spans="1:18" ht="21" customHeight="1">
@@ -4188,7 +4217,7 @@
         <v>2</v>
       </c>
       <c r="R10" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="11" spans="1:18" ht="21" customHeight="1">
@@ -4199,12 +4228,12 @@
         <v>3</v>
       </c>
       <c r="R11" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="12" spans="1:18" ht="21" customHeight="1">
       <c r="B12" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F12" s="1" t="s">
         <v>4</v>
@@ -4213,12 +4242,12 @@
         <v>4</v>
       </c>
       <c r="R12" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="13" spans="1:18" ht="21" customHeight="1">
       <c r="A13" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>4</v>
@@ -4233,7 +4262,7 @@
         <v>13</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G13" s="1" t="s">
         <v>15</v>
@@ -4248,7 +4277,7 @@
         <v>6</v>
       </c>
       <c r="R13" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="14" spans="1:18" ht="21" customHeight="1">
@@ -4259,7 +4288,7 @@
         <v>9</v>
       </c>
       <c r="R14" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="15" spans="1:18" ht="21" customHeight="1">
@@ -4323,7 +4352,7 @@
         <v>17</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>12</v>
@@ -4338,10 +4367,10 @@
         <v>17</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="Q1" s="2" t="s">
         <v>7</v>
@@ -4349,7 +4378,7 @@
     </row>
     <row r="2" spans="1:18" ht="21" customHeight="1">
       <c r="E2" s="1" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>8</v>
@@ -4361,7 +4390,7 @@
         <v>1</v>
       </c>
       <c r="R2" s="4" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
     </row>
     <row r="3" spans="1:18" ht="21" customHeight="1">
@@ -4372,10 +4401,10 @@
         <v>8</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>17</v>
@@ -4390,7 +4419,7 @@
         <v>5</v>
       </c>
       <c r="R3" s="4" t="s">
-        <v>115</v>
+        <v>105</v>
       </c>
     </row>
     <row r="4" spans="1:18" ht="21" customHeight="1">
@@ -4410,7 +4439,7 @@
         <v>7</v>
       </c>
       <c r="R4" s="4" t="s">
-        <v>116</v>
+        <v>106</v>
       </c>
     </row>
     <row r="5" spans="1:18" ht="21" customHeight="1">
@@ -4430,7 +4459,7 @@
         <v>9</v>
       </c>
       <c r="R5" s="4" t="s">
-        <v>117</v>
+        <v>107</v>
       </c>
     </row>
     <row r="6" spans="1:18" ht="21" customHeight="1">
@@ -4450,7 +4479,7 @@
         <v>10</v>
       </c>
       <c r="R6" s="4" t="s">
-        <v>118</v>
+        <v>108</v>
       </c>
     </row>
     <row r="7" spans="1:18" ht="21" customHeight="1">
@@ -4473,7 +4502,7 @@
         <v>8</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="M7" s="1" t="s">
         <v>14</v>
@@ -4490,7 +4519,7 @@
         <v>5</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="9" spans="1:18" ht="21" customHeight="1">
@@ -4510,7 +4539,7 @@
         <v>15</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H9" s="1" t="s">
         <v>15</v>
@@ -4519,7 +4548,7 @@
         <v>12</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K9" s="1" t="s">
         <v>17</v>
@@ -4528,7 +4557,7 @@
         <v>17</v>
       </c>
       <c r="Q9" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="10" spans="1:18" ht="21" customHeight="1">
@@ -4536,13 +4565,13 @@
         <v>15</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q10" s="3">
         <v>2</v>
       </c>
       <c r="R10" s="4" t="s">
-        <v>119</v>
+        <v>222</v>
       </c>
     </row>
     <row r="11" spans="1:18" ht="21" customHeight="1">
@@ -4556,7 +4585,7 @@
         <v>3</v>
       </c>
       <c r="R11" s="4" t="s">
-        <v>120</v>
+        <v>109</v>
       </c>
     </row>
     <row r="12" spans="1:18" ht="21" customHeight="1">
@@ -4588,7 +4617,7 @@
         <v>4</v>
       </c>
       <c r="R12" s="4" t="s">
-        <v>121</v>
+        <v>110</v>
       </c>
     </row>
     <row r="13" spans="1:18" ht="21" customHeight="1">
@@ -4599,18 +4628,18 @@
         <v>6</v>
       </c>
       <c r="R13" s="4" t="s">
-        <v>122</v>
+        <v>223</v>
       </c>
     </row>
     <row r="14" spans="1:18" ht="21" customHeight="1">
       <c r="K14" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q14" s="3">
         <v>8</v>
       </c>
       <c r="R14" s="4" t="s">
-        <v>123</v>
+        <v>111</v>
       </c>
     </row>
     <row r="15" spans="1:18" ht="21" customHeight="1"/>
@@ -4651,7 +4680,7 @@
   <sheetData>
     <row r="1" spans="1:18" ht="21" customHeight="1">
       <c r="E1" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="Q1" s="2" t="s">
         <v>7</v>
@@ -4668,7 +4697,7 @@
         <v>3</v>
       </c>
       <c r="R2" s="4" t="s">
-        <v>124</v>
+        <v>112</v>
       </c>
     </row>
     <row r="3" spans="1:18" ht="21" customHeight="1">
@@ -4688,7 +4717,7 @@
         <v>17</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J3" s="1" t="s">
         <v>12</v>
@@ -4697,24 +4726,24 @@
         <v>7</v>
       </c>
       <c r="R3" s="4" t="s">
-        <v>125</v>
+        <v>113</v>
       </c>
     </row>
     <row r="4" spans="1:18" ht="21" customHeight="1">
       <c r="E4" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G4" s="1" t="s">
         <v>11</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Q4" s="3">
         <v>8</v>
       </c>
       <c r="R4" s="4" t="s">
-        <v>126</v>
+        <v>114</v>
       </c>
     </row>
     <row r="5" spans="1:18" ht="21" customHeight="1">
@@ -4731,7 +4760,7 @@
         <v>9</v>
       </c>
       <c r="R5" s="4" t="s">
-        <v>127</v>
+        <v>115</v>
       </c>
     </row>
     <row r="6" spans="1:18" ht="21" customHeight="1">
@@ -4748,18 +4777,18 @@
         <v>10</v>
       </c>
       <c r="R6" s="4" t="s">
-        <v>128</v>
+        <v>116</v>
       </c>
     </row>
     <row r="7" spans="1:18" ht="21" customHeight="1">
       <c r="D7" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="G7" s="1" t="s">
         <v>12</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="8" spans="1:18" ht="21" customHeight="1">
@@ -4767,7 +4796,7 @@
         <v>12</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="9" spans="1:18" ht="21" customHeight="1">
@@ -4781,7 +4810,7 @@
         <v>11</v>
       </c>
       <c r="Q9" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="10" spans="1:18" ht="21" customHeight="1">
@@ -4795,7 +4824,7 @@
         <v>14</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G10" s="1" t="s">
         <v>8</v>
@@ -4816,12 +4845,12 @@
         <v>1</v>
       </c>
       <c r="R10" s="4" t="s">
-        <v>129</v>
+        <v>117</v>
       </c>
     </row>
     <row r="11" spans="1:18" ht="21" customHeight="1">
       <c r="D11" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G11" s="1" t="s">
         <v>17</v>
@@ -4833,7 +4862,7 @@
         <v>2</v>
       </c>
       <c r="R11" s="4" t="s">
-        <v>130</v>
+        <v>118</v>
       </c>
     </row>
     <row r="12" spans="1:18" ht="21" customHeight="1">
@@ -4844,13 +4873,13 @@
         <v>12</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>15</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F12" s="1" t="s">
         <v>5</v>
@@ -4859,13 +4888,13 @@
         <v>12</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Q12" s="3">
         <v>4</v>
       </c>
       <c r="R12" s="4" t="s">
-        <v>131</v>
+        <v>224</v>
       </c>
     </row>
     <row r="13" spans="1:18" ht="21" customHeight="1">
@@ -4879,7 +4908,7 @@
         <v>5</v>
       </c>
       <c r="R13" s="4" t="s">
-        <v>132</v>
+        <v>119</v>
       </c>
     </row>
     <row r="14" spans="1:18" ht="21" customHeight="1">
@@ -4887,18 +4916,18 @@
         <v>12</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Q14" s="3">
         <v>6</v>
       </c>
       <c r="R14" s="4" t="s">
-        <v>133</v>
+        <v>120</v>
       </c>
     </row>
     <row r="15" spans="1:18" ht="21" customHeight="1">
       <c r="J15" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="16" spans="1:18" ht="21" customHeight="1">
@@ -4955,13 +4984,13 @@
         <v>9</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="I21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K21" s="1" t="s">
         <v>8</v>
@@ -5042,7 +5071,7 @@
         <v>2</v>
       </c>
       <c r="R2" s="4" t="s">
-        <v>134</v>
+        <v>121</v>
       </c>
     </row>
     <row r="3" spans="1:18" ht="21" customHeight="1">
@@ -5053,7 +5082,7 @@
         <v>3</v>
       </c>
       <c r="R3" s="4" t="s">
-        <v>120</v>
+        <v>225</v>
       </c>
     </row>
     <row r="4" spans="1:18" ht="21" customHeight="1">
@@ -5064,7 +5093,7 @@
         <v>5</v>
       </c>
       <c r="R4" s="4" t="s">
-        <v>135</v>
+        <v>122</v>
       </c>
     </row>
     <row r="5" spans="1:18" ht="21" customHeight="1">
@@ -5096,7 +5125,7 @@
         <v>8</v>
       </c>
       <c r="R5" s="4" t="s">
-        <v>136</v>
+        <v>123</v>
       </c>
     </row>
     <row r="6" spans="1:18" ht="21" customHeight="1">
@@ -5110,7 +5139,7 @@
         <v>10</v>
       </c>
       <c r="R6" s="4" t="s">
-        <v>137</v>
+        <v>124</v>
       </c>
     </row>
     <row r="7" spans="1:18" ht="21" customHeight="1">
@@ -5121,7 +5150,7 @@
         <v>12</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I7" s="1" t="s">
         <v>17</v>
@@ -5133,7 +5162,7 @@
         <v>4</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="8" spans="1:18" ht="21" customHeight="1">
@@ -5155,10 +5184,10 @@
         <v>9</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="Q9" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="10" spans="1:18" ht="21" customHeight="1">
@@ -5190,13 +5219,13 @@
         <v>4</v>
       </c>
       <c r="M10" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Q10" s="3">
         <v>1</v>
       </c>
       <c r="R10" s="4" t="s">
-        <v>138</v>
+        <v>125</v>
       </c>
     </row>
     <row r="11" spans="1:18" ht="21" customHeight="1">
@@ -5204,7 +5233,7 @@
         <v>17</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="K11" s="1" t="s">
         <v>12</v>
@@ -5213,12 +5242,12 @@
         <v>4</v>
       </c>
       <c r="R11" s="4" t="s">
-        <v>139</v>
+        <v>126</v>
       </c>
     </row>
     <row r="12" spans="1:18" ht="21" customHeight="1">
       <c r="E12" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H12" s="1" t="s">
         <v>4</v>
@@ -5230,7 +5259,7 @@
         <v>6</v>
       </c>
       <c r="R12" s="4" t="s">
-        <v>140</v>
+        <v>127</v>
       </c>
     </row>
     <row r="13" spans="1:18" ht="21" customHeight="1">
@@ -5244,7 +5273,7 @@
         <v>7</v>
       </c>
       <c r="R13" s="4" t="s">
-        <v>141</v>
+        <v>128</v>
       </c>
     </row>
     <row r="14" spans="1:18" ht="21" customHeight="1">
@@ -5258,7 +5287,7 @@
         <v>9</v>
       </c>
       <c r="R14" s="4" t="s">
-        <v>142</v>
+        <v>129</v>
       </c>
     </row>
     <row r="15" spans="1:18" ht="21" customHeight="1">
@@ -5292,15 +5321,15 @@
         <v>5</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="17" spans="6:8" ht="21" customHeight="1">
       <c r="F17" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="18" spans="6:8" ht="21" customHeight="1"/>
@@ -5338,7 +5367,7 @@
   <sheetData>
     <row r="1" spans="1:18" ht="21" customHeight="1">
       <c r="C1" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Q1" s="2" t="s">
         <v>7</v>
@@ -5370,7 +5399,7 @@
         <v>2</v>
       </c>
       <c r="R2" s="4" t="s">
-        <v>143</v>
+        <v>130</v>
       </c>
     </row>
     <row r="3" spans="1:18" ht="21" customHeight="1">
@@ -5381,7 +5410,7 @@
         <v>3</v>
       </c>
       <c r="R3" s="4" t="s">
-        <v>144</v>
+        <v>131</v>
       </c>
     </row>
     <row r="4" spans="1:18" ht="21" customHeight="1">
@@ -5395,7 +5424,7 @@
         <v>15</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>12</v>
@@ -5404,18 +5433,18 @@
         <v>4</v>
       </c>
       <c r="R4" s="4" t="s">
-        <v>145</v>
+        <v>132</v>
       </c>
     </row>
     <row r="5" spans="1:18" ht="21" customHeight="1">
       <c r="C5" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="Q5" s="3">
         <v>9</v>
       </c>
       <c r="R5" s="4" t="s">
-        <v>146</v>
+        <v>133</v>
       </c>
     </row>
     <row r="6" spans="1:18" ht="21" customHeight="1">
@@ -5423,7 +5452,7 @@
         <v>12</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>20</v>
@@ -5438,7 +5467,7 @@
         <v>4</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J6" s="1" t="s">
         <v>2</v>
@@ -5447,7 +5476,7 @@
         <v>12</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="M6" s="1" t="s">
         <v>17</v>
@@ -5456,7 +5485,7 @@
         <v>10</v>
       </c>
       <c r="R6" s="4" t="s">
-        <v>147</v>
+        <v>134</v>
       </c>
     </row>
     <row r="7" spans="1:18" ht="21" customHeight="1">
@@ -5464,12 +5493,12 @@
         <v>12</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
     </row>
     <row r="8" spans="1:18" ht="21" customHeight="1">
       <c r="G8" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="K8" s="1" t="s">
         <v>12</v>
@@ -5483,7 +5512,7 @@
         <v>9</v>
       </c>
       <c r="Q9" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="10" spans="1:18" ht="21" customHeight="1">
@@ -5497,13 +5526,13 @@
         <v>15</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="Q10" s="3">
         <v>1</v>
       </c>
       <c r="R10" s="4" t="s">
-        <v>148</v>
+        <v>135</v>
       </c>
     </row>
     <row r="11" spans="1:18" ht="21" customHeight="1">
@@ -5511,10 +5540,10 @@
         <v>20</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K11" s="1" t="s">
         <v>15</v>
@@ -5523,7 +5552,7 @@
         <v>5</v>
       </c>
       <c r="R11" s="4" t="s">
-        <v>149</v>
+        <v>136</v>
       </c>
     </row>
     <row r="12" spans="1:18" ht="21" customHeight="1">
@@ -5543,7 +5572,7 @@
         <v>6</v>
       </c>
       <c r="R12" s="4" t="s">
-        <v>150</v>
+        <v>137</v>
       </c>
     </row>
     <row r="13" spans="1:18" ht="21" customHeight="1">
@@ -5563,7 +5592,7 @@
         <v>7</v>
       </c>
       <c r="R13" s="4" t="s">
-        <v>151</v>
+        <v>138</v>
       </c>
     </row>
     <row r="14" spans="1:18" ht="21" customHeight="1">
@@ -5592,7 +5621,7 @@
         <v>8</v>
       </c>
       <c r="R14" s="4" t="s">
-        <v>152</v>
+        <v>139</v>
       </c>
     </row>
     <row r="15" spans="1:18" ht="21" customHeight="1">
@@ -5688,19 +5717,19 @@
         <v>14</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>17</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>15</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K1" s="1" t="s">
         <v>14</v>
@@ -5720,7 +5749,7 @@
         <v>1</v>
       </c>
       <c r="R2" s="4" t="s">
-        <v>153</v>
+        <v>140</v>
       </c>
     </row>
     <row r="3" spans="1:18" ht="21" customHeight="1">
@@ -5734,7 +5763,7 @@
         <v>4</v>
       </c>
       <c r="R3" s="4" t="s">
-        <v>154</v>
+        <v>141</v>
       </c>
     </row>
     <row r="4" spans="1:18" ht="21" customHeight="1">
@@ -5748,7 +5777,7 @@
         <v>7</v>
       </c>
       <c r="R4" s="4" t="s">
-        <v>155</v>
+        <v>142</v>
       </c>
     </row>
     <row r="5" spans="1:18" ht="21" customHeight="1">
@@ -5756,13 +5785,13 @@
         <v>12</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q5" s="3">
         <v>8</v>
       </c>
       <c r="R5" s="4" t="s">
-        <v>156</v>
+        <v>143</v>
       </c>
     </row>
     <row r="6" spans="1:18" ht="21" customHeight="1">
@@ -5770,13 +5799,13 @@
         <v>8</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>8</v>
@@ -5785,7 +5814,7 @@
         <v>9</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="J6" s="1" t="s">
         <v>17</v>
@@ -5794,7 +5823,7 @@
         <v>9</v>
       </c>
       <c r="R6" s="4" t="s">
-        <v>157</v>
+        <v>144</v>
       </c>
     </row>
     <row r="7" spans="1:18" ht="21" customHeight="1">
@@ -5815,7 +5844,7 @@
     </row>
     <row r="9" spans="1:18" ht="21" customHeight="1">
       <c r="B9" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>9</v>
@@ -5824,12 +5853,12 @@
         <v>13</v>
       </c>
       <c r="Q9" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="10" spans="1:18" ht="21" customHeight="1">
       <c r="B10" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>12</v>
@@ -5841,7 +5870,7 @@
         <v>2</v>
       </c>
       <c r="R10" s="4" t="s">
-        <v>158</v>
+        <v>145</v>
       </c>
     </row>
     <row r="11" spans="1:18" ht="21" customHeight="1">
@@ -5855,10 +5884,10 @@
         <v>0</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>15</v>
@@ -5882,7 +5911,7 @@
         <v>3</v>
       </c>
       <c r="R11" s="4" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
     </row>
     <row r="12" spans="1:18" ht="21" customHeight="1">
@@ -5896,7 +5925,7 @@
         <v>5</v>
       </c>
       <c r="R12" s="4" t="s">
-        <v>160</v>
+        <v>147</v>
       </c>
     </row>
     <row r="13" spans="1:18" ht="21" customHeight="1">
@@ -5904,24 +5933,24 @@
         <v>15</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Q13" s="3">
         <v>6</v>
       </c>
       <c r="R13" s="4" t="s">
-        <v>161</v>
+        <v>148</v>
       </c>
     </row>
     <row r="14" spans="1:18" ht="21" customHeight="1">
       <c r="B14" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>17</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F14" s="1" t="s">
         <v>9</v>
@@ -5936,13 +5965,13 @@
         <v>14</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q14" s="3">
         <v>10</v>
       </c>
       <c r="R14" s="4" t="s">
-        <v>162</v>
+        <v>149</v>
       </c>
     </row>
     <row r="15" spans="1:18" ht="21" customHeight="1">
@@ -5975,12 +6004,12 @@
         <v>5</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
     </row>
     <row r="18" spans="2:7" ht="21" customHeight="1">
       <c r="G18" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="19" spans="2:7" ht="21" customHeight="1">
@@ -6005,7 +6034,7 @@
     </row>
     <row r="23" spans="2:7" ht="21" customHeight="1">
       <c r="G23" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="24" spans="2:7" ht="21" customHeight="1">
@@ -6041,13 +6070,13 @@
   <sheetData>
     <row r="1" spans="1:18" ht="21" customHeight="1">
       <c r="B1" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>17</v>
@@ -6067,13 +6096,13 @@
     </row>
     <row r="2" spans="1:18" ht="21" customHeight="1">
       <c r="E2" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q2" s="3">
         <v>1</v>
       </c>
       <c r="R2" s="4" t="s">
-        <v>163</v>
+        <v>150</v>
       </c>
     </row>
     <row r="3" spans="1:18" ht="21" customHeight="1">
@@ -6084,7 +6113,7 @@
         <v>3</v>
       </c>
       <c r="R3" s="4" t="s">
-        <v>164</v>
+        <v>151</v>
       </c>
     </row>
     <row r="4" spans="1:18" ht="21" customHeight="1">
@@ -6113,7 +6142,7 @@
         <v>5</v>
       </c>
       <c r="R4" s="4" t="s">
-        <v>165</v>
+        <v>152</v>
       </c>
     </row>
     <row r="5" spans="1:18" ht="21" customHeight="1">
@@ -6124,7 +6153,7 @@
         <v>7</v>
       </c>
       <c r="R5" s="4" t="s">
-        <v>166</v>
+        <v>153</v>
       </c>
     </row>
     <row r="6" spans="1:18" ht="21" customHeight="1">
@@ -6132,13 +6161,13 @@
         <v>15</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q6" s="3">
         <v>9</v>
       </c>
       <c r="R6" s="4" t="s">
-        <v>167</v>
+        <v>154</v>
       </c>
     </row>
     <row r="7" spans="1:18" ht="21" customHeight="1">
@@ -6174,18 +6203,18 @@
         <v>9</v>
       </c>
       <c r="Q9" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="10" spans="1:18" ht="21" customHeight="1">
       <c r="B10" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>12</v>
@@ -6209,24 +6238,24 @@
         <v>2</v>
       </c>
       <c r="R10" s="4" t="s">
-        <v>168</v>
+        <v>155</v>
       </c>
     </row>
     <row r="11" spans="1:18" ht="21" customHeight="1">
       <c r="B11" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>2</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="Q11" s="3">
         <v>4</v>
       </c>
       <c r="R11" s="4" t="s">
-        <v>169</v>
+        <v>156</v>
       </c>
     </row>
     <row r="12" spans="1:18" ht="21" customHeight="1">
@@ -6240,7 +6269,7 @@
         <v>6</v>
       </c>
       <c r="R12" s="4" t="s">
-        <v>170</v>
+        <v>157</v>
       </c>
     </row>
     <row r="13" spans="1:18" ht="21" customHeight="1">
@@ -6254,7 +6283,7 @@
         <v>8</v>
       </c>
       <c r="R13" s="4" t="s">
-        <v>171</v>
+        <v>158</v>
       </c>
     </row>
     <row r="14" spans="1:18" ht="21" customHeight="1">
@@ -6268,7 +6297,7 @@
         <v>9</v>
       </c>
       <c r="R14" s="4" t="s">
-        <v>172</v>
+        <v>159</v>
       </c>
     </row>
     <row r="15" spans="1:18" ht="21" customHeight="1">
@@ -6276,13 +6305,13 @@
         <v>8</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>0</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="E15" s="1" t="s">
         <v>12</v>
@@ -6296,7 +6325,7 @@
     </row>
     <row r="16" spans="1:18" ht="21" customHeight="1">
       <c r="A16" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E16" s="1" t="s">
         <v>9</v>
@@ -6307,7 +6336,7 @@
     </row>
     <row r="17" spans="1:8" ht="21" customHeight="1">
       <c r="A17" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H17" s="1" t="s">
         <v>1</v>
@@ -6325,7 +6354,7 @@
     </row>
     <row r="20" spans="1:8" ht="21" customHeight="1">
       <c r="A20" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="21" customHeight="1">
@@ -6335,7 +6364,7 @@
     </row>
     <row r="22" spans="1:8" ht="21" customHeight="1">
       <c r="A22" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="23" spans="1:8" ht="21" customHeight="1">
@@ -6395,7 +6424,7 @@
         <v>9</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I2" s="1" t="s">
         <v>2</v>
@@ -6404,7 +6433,7 @@
         <v>12</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L2" s="1" t="s">
         <v>17</v>
@@ -6413,7 +6442,7 @@
         <v>2</v>
       </c>
       <c r="R2" s="4" t="s">
-        <v>173</v>
+        <v>160</v>
       </c>
     </row>
     <row r="3" spans="1:18" ht="21" customHeight="1">
@@ -6421,13 +6450,13 @@
         <v>8</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q3" s="3">
         <v>5</v>
       </c>
       <c r="R3" s="4" t="s">
-        <v>174</v>
+        <v>161</v>
       </c>
     </row>
     <row r="4" spans="1:18" ht="21" customHeight="1">
@@ -6441,7 +6470,7 @@
         <v>7</v>
       </c>
       <c r="R4" s="4" t="s">
-        <v>175</v>
+        <v>162</v>
       </c>
     </row>
     <row r="5" spans="1:18" ht="21" customHeight="1">
@@ -6458,7 +6487,7 @@
         <v>8</v>
       </c>
       <c r="R5" s="4" t="s">
-        <v>176</v>
+        <v>163</v>
       </c>
     </row>
     <row r="6" spans="1:18" ht="21" customHeight="1">
@@ -6487,7 +6516,7 @@
         <v>8</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J6" s="1" t="s">
         <v>17</v>
@@ -6499,15 +6528,15 @@
         <v>10</v>
       </c>
       <c r="R6" s="4" t="s">
-        <v>177</v>
+        <v>164</v>
       </c>
     </row>
     <row r="7" spans="1:18" ht="21" customHeight="1">
       <c r="B7" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I7" s="1" t="s">
         <v>12</v>
@@ -6521,7 +6550,7 @@
         <v>13</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L8" s="1" t="s">
         <v>4</v>
@@ -6550,7 +6579,7 @@
         <v>1</v>
       </c>
       <c r="Q9" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="10" spans="1:18" ht="21" customHeight="1">
@@ -6567,7 +6596,7 @@
         <v>1</v>
       </c>
       <c r="R10" s="4" t="s">
-        <v>178</v>
+        <v>165</v>
       </c>
     </row>
     <row r="11" spans="1:18" ht="21" customHeight="1">
@@ -6581,7 +6610,7 @@
         <v>3</v>
       </c>
       <c r="R11" s="4" t="s">
-        <v>179</v>
+        <v>166</v>
       </c>
     </row>
     <row r="12" spans="1:18" ht="21" customHeight="1">
@@ -6595,18 +6624,18 @@
         <v>4</v>
       </c>
       <c r="R12" s="4" t="s">
-        <v>180</v>
+        <v>167</v>
       </c>
     </row>
     <row r="13" spans="1:18" ht="21" customHeight="1">
       <c r="C13" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>4</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>17</v>
@@ -6636,7 +6665,7 @@
         <v>6</v>
       </c>
       <c r="R13" s="4" t="s">
-        <v>181</v>
+        <v>168</v>
       </c>
     </row>
     <row r="14" spans="1:18" ht="21" customHeight="1">
@@ -6644,13 +6673,13 @@
         <v>1</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="Q14" s="3">
         <v>9</v>
       </c>
       <c r="R14" s="4" t="s">
-        <v>182</v>
+        <v>169</v>
       </c>
     </row>
     <row r="15" spans="1:18" ht="21" customHeight="1">
@@ -6685,7 +6714,7 @@
     </row>
     <row r="21" spans="4:10" ht="21" customHeight="1">
       <c r="D21" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E21" s="1" t="s">
         <v>12</v>
@@ -6703,7 +6732,7 @@
         <v>15</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="22" spans="4:10" ht="21" customHeight="1">
@@ -6755,10 +6784,10 @@
         <v>8</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>15</v>
@@ -6767,7 +6796,7 @@
         <v>12</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H2" s="1" t="s">
         <v>17</v>
@@ -6782,7 +6811,7 @@
         <v>3</v>
       </c>
       <c r="R2" s="4" t="s">
-        <v>183</v>
+        <v>170</v>
       </c>
     </row>
     <row r="3" spans="2:18" ht="21" customHeight="1">
@@ -6799,7 +6828,7 @@
         <v>5</v>
       </c>
       <c r="R3" s="4" t="s">
-        <v>184</v>
+        <v>171</v>
       </c>
     </row>
     <row r="4" spans="2:18" ht="21" customHeight="1">
@@ -6813,19 +6842,19 @@
         <v>12</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>185</v>
+        <v>172</v>
       </c>
       <c r="H4" s="1" t="s">
         <v>13</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="J4" s="1" t="s">
         <v>15</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L4" s="1" t="s">
         <v>12</v>
@@ -6834,7 +6863,7 @@
         <v>6</v>
       </c>
       <c r="R4" s="4" t="s">
-        <v>186</v>
+        <v>173</v>
       </c>
     </row>
     <row r="5" spans="2:18" ht="21" customHeight="1">
@@ -6845,13 +6874,13 @@
         <v>17</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="Q5" s="3">
         <v>8</v>
       </c>
       <c r="R5" s="4" t="s">
-        <v>187</v>
+        <v>174</v>
       </c>
     </row>
     <row r="6" spans="2:18" ht="21" customHeight="1">
@@ -6868,7 +6897,7 @@
         <v>10</v>
       </c>
       <c r="R6" s="4" t="s">
-        <v>188</v>
+        <v>175</v>
       </c>
     </row>
     <row r="7" spans="2:18" ht="21" customHeight="1">
@@ -6896,7 +6925,7 @@
         <v>14</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L8" s="1" t="s">
         <v>5</v>
@@ -6904,10 +6933,10 @@
     </row>
     <row r="9" spans="2:18" ht="21" customHeight="1">
       <c r="H9" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="Q9" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="10" spans="2:18" ht="21" customHeight="1">
@@ -6918,18 +6947,18 @@
         <v>1</v>
       </c>
       <c r="R10" s="4" t="s">
-        <v>189</v>
+        <v>176</v>
       </c>
     </row>
     <row r="11" spans="2:18" ht="21" customHeight="1">
       <c r="B11" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>17</v>
@@ -6941,7 +6970,7 @@
         <v>4</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I11" s="1" t="s">
         <v>8</v>
@@ -6956,7 +6985,7 @@
         <v>2</v>
       </c>
       <c r="R11" s="4" t="s">
-        <v>190</v>
+        <v>177</v>
       </c>
     </row>
     <row r="12" spans="2:18" ht="21" customHeight="1">
@@ -6970,7 +6999,7 @@
         <v>4</v>
       </c>
       <c r="R12" s="4" t="s">
-        <v>191</v>
+        <v>178</v>
       </c>
     </row>
     <row r="13" spans="2:18" ht="21" customHeight="1">
@@ -6984,7 +7013,7 @@
         <v>7</v>
       </c>
       <c r="R13" s="4" t="s">
-        <v>192</v>
+        <v>179</v>
       </c>
     </row>
     <row r="14" spans="2:18" ht="21" customHeight="1">
@@ -6998,7 +7027,7 @@
         <v>9</v>
       </c>
       <c r="R14" s="4" t="s">
-        <v>193</v>
+        <v>180</v>
       </c>
     </row>
     <row r="15" spans="2:18" ht="21" customHeight="1">
@@ -7080,7 +7109,7 @@
   <sheetData>
     <row r="1" spans="1:18" ht="21" customHeight="1">
       <c r="J1" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="Q1" s="2" t="s">
         <v>7</v>
@@ -7088,7 +7117,7 @@
     </row>
     <row r="2" spans="1:18" ht="21" customHeight="1">
       <c r="D2" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J2" s="1" t="s">
         <v>4</v>
@@ -7100,12 +7129,12 @@
         <v>4</v>
       </c>
       <c r="R2" s="4" t="s">
-        <v>194</v>
+        <v>181</v>
       </c>
     </row>
     <row r="3" spans="1:18" ht="21" customHeight="1">
       <c r="C3" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>8</v>
@@ -7117,10 +7146,10 @@
         <v>12</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="I3" s="1" t="s">
         <v>8</v>
@@ -7129,13 +7158,13 @@
         <v>9</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="Q3" s="3">
         <v>5</v>
       </c>
       <c r="R3" s="4" t="s">
-        <v>195</v>
+        <v>182</v>
       </c>
     </row>
     <row r="4" spans="1:18" ht="21" customHeight="1">
@@ -7146,13 +7175,13 @@
         <v>9</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="Q4" s="3">
         <v>6</v>
       </c>
       <c r="R4" s="4" t="s">
-        <v>196</v>
+        <v>183</v>
       </c>
     </row>
     <row r="5" spans="1:18" ht="21" customHeight="1">
@@ -7175,7 +7204,7 @@
         <v>14</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H5" s="1" t="s">
         <v>17</v>
@@ -7190,7 +7219,7 @@
         <v>7</v>
       </c>
       <c r="R5" s="4" t="s">
-        <v>197</v>
+        <v>184</v>
       </c>
     </row>
     <row r="6" spans="1:18" ht="21" customHeight="1">
@@ -7201,13 +7230,13 @@
         <v>0</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="Q6" s="3">
         <v>9</v>
       </c>
       <c r="R6" s="4" t="s">
-        <v>198</v>
+        <v>185</v>
       </c>
     </row>
     <row r="7" spans="1:18" ht="21" customHeight="1">
@@ -7226,7 +7255,7 @@
         <v>4</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="9" spans="1:18" ht="21" customHeight="1">
@@ -7243,7 +7272,7 @@
         <v>12</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K9" s="1" t="s">
         <v>14</v>
@@ -7252,10 +7281,10 @@
         <v>17</v>
       </c>
       <c r="M9" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q9" s="2" t="s">
         <v>23</v>
-      </c>
-      <c r="Q9" s="2" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="10" spans="1:18" ht="21" customHeight="1">
@@ -7263,7 +7292,7 @@
         <v>8</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="L10" s="1" t="s">
         <v>8</v>
@@ -7272,7 +7301,7 @@
         <v>1</v>
       </c>
       <c r="R10" s="4" t="s">
-        <v>199</v>
+        <v>186</v>
       </c>
     </row>
     <row r="11" spans="1:18" ht="21" customHeight="1">
@@ -7280,10 +7309,10 @@
         <v>4</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H11" s="1" t="s">
         <v>13</v>
@@ -7298,7 +7327,7 @@
         <v>2</v>
       </c>
       <c r="R11" s="4" t="s">
-        <v>200</v>
+        <v>187</v>
       </c>
     </row>
     <row r="12" spans="1:18" ht="21" customHeight="1">
@@ -7312,7 +7341,7 @@
         <v>3</v>
       </c>
       <c r="R12" s="4" t="s">
-        <v>201</v>
+        <v>188</v>
       </c>
     </row>
     <row r="13" spans="1:18" ht="21" customHeight="1">
@@ -7326,7 +7355,7 @@
         <v>6</v>
       </c>
       <c r="R13" s="4" t="s">
-        <v>202</v>
+        <v>226</v>
       </c>
     </row>
     <row r="14" spans="1:18" ht="21" customHeight="1">
@@ -7337,7 +7366,7 @@
         <v>8</v>
       </c>
       <c r="R14" s="4" t="s">
-        <v>203</v>
+        <v>189</v>
       </c>
     </row>
     <row r="15" spans="1:18" ht="21" customHeight="1">
@@ -7365,7 +7394,7 @@
         <v>15</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G16" s="1" t="s">
         <v>13</v>
@@ -7382,7 +7411,7 @@
     </row>
     <row r="17" spans="2:6" ht="21" customHeight="1">
       <c r="B17" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F17" s="1" t="s">
         <v>12</v>
@@ -7443,7 +7472,7 @@
   <sheetData>
     <row r="1" spans="1:18" ht="21" customHeight="1">
       <c r="C1" s="1" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>12</v>
@@ -7455,7 +7484,7 @@
         <v>14</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>17</v>
@@ -7478,7 +7507,7 @@
         <v>1</v>
       </c>
       <c r="R2" s="4" t="s">
-        <v>204</v>
+        <v>190</v>
       </c>
     </row>
     <row r="3" spans="1:18" ht="21" customHeight="1">
@@ -7498,13 +7527,13 @@
         <v>12</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Q3" s="3">
         <v>4</v>
       </c>
       <c r="R3" s="4" t="s">
-        <v>205</v>
+        <v>191</v>
       </c>
     </row>
     <row r="4" spans="1:18" ht="21" customHeight="1">
@@ -7521,12 +7550,12 @@
         <v>6</v>
       </c>
       <c r="R4" s="4" t="s">
-        <v>206</v>
+        <v>192</v>
       </c>
     </row>
     <row r="5" spans="1:18" ht="21" customHeight="1">
       <c r="C5" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>11</v>
@@ -7538,7 +7567,7 @@
         <v>8</v>
       </c>
       <c r="R5" s="4" t="s">
-        <v>207</v>
+        <v>193</v>
       </c>
     </row>
     <row r="6" spans="1:18" ht="21" customHeight="1">
@@ -7552,7 +7581,7 @@
         <v>9</v>
       </c>
       <c r="R6" s="4" t="s">
-        <v>208</v>
+        <v>194</v>
       </c>
     </row>
     <row r="7" spans="1:18" ht="21" customHeight="1">
@@ -7572,7 +7601,7 @@
         <v>8</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I7" s="1" t="s">
         <v>17</v>
@@ -7600,7 +7629,7 @@
         <v>17</v>
       </c>
       <c r="Q9" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="10" spans="1:18" ht="21" customHeight="1">
@@ -7611,7 +7640,7 @@
         <v>1</v>
       </c>
       <c r="R10" s="4" t="s">
-        <v>209</v>
+        <v>195</v>
       </c>
     </row>
     <row r="11" spans="1:18" ht="21" customHeight="1">
@@ -7625,12 +7654,12 @@
         <v>2</v>
       </c>
       <c r="R11" s="4" t="s">
-        <v>210</v>
+        <v>196</v>
       </c>
     </row>
     <row r="12" spans="1:18" ht="21" customHeight="1">
       <c r="A12" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>8</v>
@@ -7654,7 +7683,7 @@
         <v>3</v>
       </c>
       <c r="R12" s="4" t="s">
-        <v>211</v>
+        <v>197</v>
       </c>
     </row>
     <row r="13" spans="1:18" ht="21" customHeight="1">
@@ -7668,7 +7697,7 @@
         <v>5</v>
       </c>
       <c r="R13" s="4" t="s">
-        <v>212</v>
+        <v>198</v>
       </c>
     </row>
     <row r="14" spans="1:18" ht="21" customHeight="1">
@@ -7682,7 +7711,7 @@
         <v>7</v>
       </c>
       <c r="R14" s="4" t="s">
-        <v>213</v>
+        <v>199</v>
       </c>
     </row>
     <row r="15" spans="1:18" ht="21" customHeight="1">
@@ -7705,10 +7734,10 @@
         <v>8</v>
       </c>
       <c r="L15" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="M15" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="16" spans="1:18" ht="21" customHeight="1">
@@ -7770,7 +7799,7 @@
         <v>12</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>9</v>
@@ -7796,13 +7825,13 @@
     </row>
     <row r="2" spans="1:18" ht="21" customHeight="1">
       <c r="I2" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q2" s="3">
         <v>1</v>
       </c>
       <c r="R2" s="4" t="s">
-        <v>31</v>
+        <v>212</v>
       </c>
     </row>
     <row r="3" spans="1:18" ht="21" customHeight="1">
@@ -7813,12 +7842,12 @@
         <v>3</v>
       </c>
       <c r="R3" s="4" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4" spans="1:18" ht="21" customHeight="1">
       <c r="A4" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>15</v>
@@ -7851,12 +7880,12 @@
         <v>6</v>
       </c>
       <c r="R4" s="4" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="5" spans="1:18" ht="21" customHeight="1">
       <c r="B5" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I5" s="1" t="s">
         <v>4</v>
@@ -7868,7 +7897,7 @@
         <v>7</v>
       </c>
       <c r="R5" s="4" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="6" spans="1:18" ht="21" customHeight="1">
@@ -7894,7 +7923,7 @@
         <v>8</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="L6" s="1" t="s">
         <v>12</v>
@@ -7903,7 +7932,7 @@
         <v>8</v>
       </c>
       <c r="R6" s="4" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7" spans="1:18" ht="21" customHeight="1">
@@ -7922,7 +7951,7 @@
         <v>9</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L8" s="1" t="s">
         <v>13</v>
@@ -7936,7 +7965,7 @@
         <v>12</v>
       </c>
       <c r="Q9" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="10" spans="1:18" ht="21" customHeight="1">
@@ -7944,13 +7973,13 @@
         <v>12</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Q10" s="3">
         <v>2</v>
       </c>
       <c r="R10" s="4" t="s">
-        <v>37</v>
+        <v>213</v>
       </c>
     </row>
     <row r="11" spans="1:18" ht="21" customHeight="1">
@@ -7970,7 +7999,7 @@
         <v>12</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="J11" s="1" t="s">
         <v>15</v>
@@ -7988,7 +8017,7 @@
         <v>4</v>
       </c>
       <c r="R11" s="4" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="12" spans="1:18" ht="21" customHeight="1">
@@ -8002,7 +8031,7 @@
         <v>5</v>
       </c>
       <c r="R12" s="4" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="13" spans="1:18" ht="21" customHeight="1">
@@ -8034,7 +8063,7 @@
         <v>8</v>
       </c>
       <c r="R13" s="4" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="14" spans="1:18" ht="21" customHeight="1">
@@ -8048,7 +8077,7 @@
         <v>9</v>
       </c>
       <c r="R14" s="4" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="15" spans="1:18" ht="21" customHeight="1">
@@ -8088,7 +8117,7 @@
         <v>12</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="20" spans="5:9" ht="21" customHeight="1">
@@ -8128,7 +8157,7 @@
   <sheetData>
     <row r="1" spans="1:18" ht="21" customHeight="1">
       <c r="E1" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="Q1" s="2" t="s">
         <v>7</v>
@@ -8142,7 +8171,7 @@
         <v>12</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>17</v>
@@ -8151,10 +8180,10 @@
         <v>12</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H2" s="1" t="s">
         <v>12</v>
@@ -8163,7 +8192,7 @@
         <v>2</v>
       </c>
       <c r="R2" s="4" t="s">
-        <v>214</v>
+        <v>200</v>
       </c>
     </row>
     <row r="3" spans="1:18" ht="21" customHeight="1">
@@ -8171,7 +8200,7 @@
         <v>13</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G3" s="1" t="s">
         <v>4</v>
@@ -8180,7 +8209,7 @@
         <v>4</v>
       </c>
       <c r="R3" s="4" t="s">
-        <v>215</v>
+        <v>201</v>
       </c>
     </row>
     <row r="4" spans="1:18" ht="21" customHeight="1">
@@ -8191,13 +8220,13 @@
         <v>15</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Q4" s="3">
         <v>5</v>
       </c>
       <c r="R4" s="4" t="s">
-        <v>216</v>
+        <v>202</v>
       </c>
     </row>
     <row r="5" spans="1:18" ht="21" customHeight="1">
@@ -8205,7 +8234,7 @@
         <v>14</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="G5" s="1" t="s">
         <v>0</v>
@@ -8214,7 +8243,7 @@
         <v>8</v>
       </c>
       <c r="R5" s="4" t="s">
-        <v>217</v>
+        <v>203</v>
       </c>
     </row>
     <row r="6" spans="1:18" ht="21" customHeight="1">
@@ -8225,13 +8254,13 @@
         <v>12</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="Q6" s="3">
         <v>9</v>
       </c>
       <c r="R6" s="4" t="s">
-        <v>218</v>
+        <v>204</v>
       </c>
     </row>
     <row r="7" spans="1:18" ht="21" customHeight="1">
@@ -8268,7 +8297,7 @@
         <v>13</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L8" s="1" t="s">
         <v>15</v>
@@ -8285,7 +8314,7 @@
         <v>13</v>
       </c>
       <c r="Q9" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="10" spans="1:18" ht="21" customHeight="1">
@@ -8302,7 +8331,7 @@
         <v>15</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J10" s="1" t="s">
         <v>12</v>
@@ -8317,7 +8346,7 @@
         <v>1</v>
       </c>
       <c r="R10" s="4" t="s">
-        <v>219</v>
+        <v>205</v>
       </c>
     </row>
     <row r="11" spans="1:18" ht="21" customHeight="1">
@@ -8331,7 +8360,7 @@
         <v>2</v>
       </c>
       <c r="R11" s="4" t="s">
-        <v>220</v>
+        <v>206</v>
       </c>
     </row>
     <row r="12" spans="1:18" ht="21" customHeight="1">
@@ -8345,7 +8374,7 @@
         <v>3</v>
       </c>
       <c r="R12" s="4" t="s">
-        <v>221</v>
+        <v>207</v>
       </c>
     </row>
     <row r="13" spans="1:18" ht="21" customHeight="1">
@@ -8359,7 +8388,7 @@
         <v>6</v>
       </c>
       <c r="R13" s="4" t="s">
-        <v>222</v>
+        <v>208</v>
       </c>
     </row>
     <row r="14" spans="1:18" ht="21" customHeight="1">
@@ -8373,7 +8402,7 @@
         <v>7</v>
       </c>
       <c r="R14" s="4" t="s">
-        <v>223</v>
+        <v>209</v>
       </c>
     </row>
     <row r="15" spans="1:18" ht="21" customHeight="1">
@@ -8381,7 +8410,7 @@
         <v>4</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F15" s="1" t="s">
         <v>9</v>
@@ -8396,7 +8425,7 @@
         <v>15</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="K15" s="1" t="s">
         <v>15</v>
@@ -8424,19 +8453,19 @@
         <v>12</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>15</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G17" s="1" t="s">
         <v>15</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I17" s="1" t="s">
         <v>12</v>
@@ -8498,7 +8527,7 @@
         <v>3</v>
       </c>
       <c r="R2" s="4" t="s">
-        <v>42</v>
+        <v>214</v>
       </c>
     </row>
     <row r="3" spans="1:18" ht="21" customHeight="1">
@@ -8509,7 +8538,7 @@
         <v>9</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G3" s="1" t="s">
         <v>1</v>
@@ -8524,7 +8553,7 @@
         <v>5</v>
       </c>
       <c r="R3" s="4" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
     </row>
     <row r="4" spans="1:18" ht="21" customHeight="1">
@@ -8541,18 +8570,18 @@
         <v>6</v>
       </c>
       <c r="R4" s="4" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
     </row>
     <row r="5" spans="1:18" ht="21" customHeight="1">
       <c r="B5" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>17</v>
@@ -8561,7 +8590,7 @@
         <v>15</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H5" s="1" t="s">
         <v>13</v>
@@ -8573,7 +8602,7 @@
         <v>7</v>
       </c>
       <c r="R5" s="4" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
     <row r="6" spans="1:18" ht="21" customHeight="1">
@@ -8581,18 +8610,18 @@
         <v>5</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="Q6" s="3">
         <v>10</v>
       </c>
       <c r="R6" s="4" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
     </row>
     <row r="7" spans="1:18" ht="21" customHeight="1">
       <c r="A7" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>12</v>
@@ -8617,7 +8646,7 @@
         <v>8</v>
       </c>
       <c r="Q9" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="10" spans="1:18" ht="21" customHeight="1">
@@ -8625,7 +8654,7 @@
         <v>11</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>1</v>
@@ -8637,7 +8666,7 @@
         <v>15</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G10" s="1" t="s">
         <v>8</v>
@@ -8649,7 +8678,7 @@
         <v>1</v>
       </c>
       <c r="R10" s="4" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
     </row>
     <row r="11" spans="1:18" ht="21" customHeight="1">
@@ -8663,18 +8692,18 @@
         <v>2</v>
       </c>
       <c r="R11" s="4" t="s">
-        <v>48</v>
+        <v>215</v>
       </c>
     </row>
     <row r="12" spans="1:18" ht="21" customHeight="1">
       <c r="F12" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Q12" s="3">
         <v>4</v>
       </c>
       <c r="R12" s="4" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
     </row>
     <row r="13" spans="1:18" ht="21" customHeight="1">
@@ -8682,13 +8711,13 @@
         <v>0</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="Q13" s="3">
         <v>8</v>
       </c>
       <c r="R13" s="4" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
     </row>
     <row r="14" spans="1:18" ht="21" customHeight="1">
@@ -8696,18 +8725,18 @@
         <v>15</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Q14" s="3">
         <v>9</v>
       </c>
       <c r="R14" s="4" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="15" spans="1:18" ht="21" customHeight="1">
       <c r="F15" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="H15" s="1" t="s">
         <v>4</v>
@@ -8718,7 +8747,7 @@
         <v>12</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
     </row>
     <row r="17" spans="1:9" ht="21" customHeight="1">
@@ -8729,10 +8758,10 @@
         <v>15</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>12</v>
@@ -8757,7 +8786,7 @@
     </row>
     <row r="19" spans="1:9" ht="21" customHeight="1">
       <c r="H19" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="20" spans="1:9" ht="21" customHeight="1">
@@ -8809,7 +8838,7 @@
     </row>
     <row r="2" spans="1:18" ht="21" customHeight="1">
       <c r="B2" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>8</v>
@@ -8818,7 +8847,7 @@
         <v>3</v>
       </c>
       <c r="R2" s="4" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
     </row>
     <row r="3" spans="1:18" ht="21" customHeight="1">
@@ -8850,7 +8879,7 @@
         <v>4</v>
       </c>
       <c r="R3" s="4" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
     </row>
     <row r="4" spans="1:18" ht="21" customHeight="1">
@@ -8864,7 +8893,7 @@
         <v>7</v>
       </c>
       <c r="R4" s="4" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
     </row>
     <row r="5" spans="1:18" ht="21" customHeight="1">
@@ -8875,7 +8904,7 @@
         <v>12</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="G5" s="1" t="s">
         <v>15</v>
@@ -8890,10 +8919,10 @@
         <v>12</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="M5" s="1" t="s">
         <v>12</v>
@@ -8902,12 +8931,12 @@
         <v>8</v>
       </c>
       <c r="R5" s="4" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
     </row>
     <row r="6" spans="1:18" ht="21" customHeight="1">
       <c r="B6" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G6" s="1" t="s">
         <v>8</v>
@@ -8919,7 +8948,7 @@
         <v>10</v>
       </c>
       <c r="R6" s="4" t="s">
-        <v>59</v>
+        <v>54</v>
       </c>
     </row>
     <row r="7" spans="1:18" ht="21" customHeight="1">
@@ -8946,13 +8975,13 @@
         <v>11</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L9" s="1" t="s">
         <v>12</v>
       </c>
       <c r="Q9" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="10" spans="1:18" ht="21" customHeight="1">
@@ -8978,7 +9007,7 @@
         <v>1</v>
       </c>
       <c r="R10" s="4" t="s">
-        <v>60</v>
+        <v>217</v>
       </c>
     </row>
     <row r="11" spans="1:18" ht="21" customHeight="1">
@@ -8992,7 +9021,7 @@
         <v>2</v>
       </c>
       <c r="R11" s="4" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
     </row>
     <row r="12" spans="1:18" ht="21" customHeight="1">
@@ -9006,7 +9035,7 @@
         <v>5</v>
       </c>
       <c r="R12" s="4" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
     </row>
     <row r="13" spans="1:18" ht="21" customHeight="1">
@@ -9020,7 +9049,7 @@
         <v>14</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H13" s="1" t="s">
         <v>17</v>
@@ -9032,7 +9061,7 @@
         <v>6</v>
       </c>
       <c r="R13" s="4" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
     </row>
     <row r="14" spans="1:18" ht="21" customHeight="1">
@@ -9046,18 +9075,18 @@
         <v>9</v>
       </c>
       <c r="R14" s="4" t="s">
-        <v>21</v>
+        <v>216</v>
       </c>
     </row>
     <row r="15" spans="1:18" ht="21" customHeight="1">
       <c r="C15" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E15" s="1" t="s">
         <v>5</v>
       </c>
       <c r="L15" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="16" spans="1:18" ht="21" customHeight="1">
@@ -9080,7 +9109,7 @@
         <v>14</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="17" spans="3:3" ht="21" customHeight="1">
@@ -9147,7 +9176,7 @@
   <sheetData>
     <row r="1" spans="1:18" ht="21" customHeight="1">
       <c r="B1" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>13</v>
@@ -9162,10 +9191,10 @@
         <v>8</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>12</v>
@@ -9176,21 +9205,21 @@
     </row>
     <row r="2" spans="1:18" ht="21" customHeight="1">
       <c r="E2" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q2" s="3">
         <v>1</v>
       </c>
       <c r="R2" s="4" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
     </row>
     <row r="3" spans="1:18" ht="21" customHeight="1">
       <c r="D3" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>4</v>
@@ -9205,13 +9234,13 @@
         <v>13</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J3" s="1" t="s">
         <v>15</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="L3" s="1" t="s">
         <v>8</v>
@@ -9226,7 +9255,7 @@
         <v>4</v>
       </c>
       <c r="R3" s="4" t="s">
-        <v>65</v>
+        <v>59</v>
       </c>
     </row>
     <row r="4" spans="1:18" ht="21" customHeight="1">
@@ -9243,7 +9272,7 @@
         <v>6</v>
       </c>
       <c r="R4" s="4" t="s">
-        <v>66</v>
+        <v>218</v>
       </c>
     </row>
     <row r="5" spans="1:18" ht="21" customHeight="1">
@@ -9260,12 +9289,12 @@
         <v>8</v>
       </c>
       <c r="R5" s="4" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
     </row>
     <row r="6" spans="1:18" ht="21" customHeight="1">
       <c r="A6" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>12</v>
@@ -9277,7 +9306,7 @@
         <v>9</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="J6" s="1" t="s">
         <v>4</v>
@@ -9289,7 +9318,7 @@
         <v>10</v>
       </c>
       <c r="R6" s="4" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
     </row>
     <row r="7" spans="1:18" ht="21" customHeight="1">
@@ -9325,7 +9354,7 @@
         <v>15</v>
       </c>
       <c r="Q9" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="10" spans="1:18" ht="21" customHeight="1">
@@ -9336,7 +9365,7 @@
         <v>2</v>
       </c>
       <c r="R10" s="4" t="s">
-        <v>69</v>
+        <v>219</v>
       </c>
     </row>
     <row r="11" spans="1:18" ht="21" customHeight="1">
@@ -9344,10 +9373,10 @@
         <v>8</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>4</v>
@@ -9362,7 +9391,7 @@
         <v>4</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="K11" s="1" t="s">
         <v>8</v>
@@ -9377,7 +9406,7 @@
         <v>3</v>
       </c>
       <c r="R11" s="4" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
     </row>
     <row r="12" spans="1:18" ht="21" customHeight="1">
@@ -9388,7 +9417,7 @@
         <v>5</v>
       </c>
       <c r="R12" s="4" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
     </row>
     <row r="13" spans="1:18" ht="21" customHeight="1">
@@ -9396,13 +9425,13 @@
         <v>5</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="Q13" s="3">
         <v>7</v>
       </c>
       <c r="R13" s="4" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
     </row>
     <row r="14" spans="1:18" ht="21" customHeight="1">
@@ -9410,7 +9439,7 @@
         <v>12</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>11</v>
@@ -9422,7 +9451,7 @@
         <v>8</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I14" s="1" t="s">
         <v>8</v>
@@ -9437,18 +9466,18 @@
         <v>4</v>
       </c>
       <c r="M14" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Q14" s="3">
         <v>9</v>
       </c>
       <c r="R14" s="4" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
     </row>
     <row r="15" spans="1:18" ht="21" customHeight="1">
       <c r="L15" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="16" spans="1:18" ht="21" customHeight="1">
@@ -9458,7 +9487,7 @@
     </row>
     <row r="17" spans="12:12" ht="21" customHeight="1">
       <c r="L17" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="18" spans="12:12" ht="21" customHeight="1">
@@ -9473,12 +9502,12 @@
     </row>
     <row r="20" spans="12:12" ht="21" customHeight="1">
       <c r="L20" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="21" spans="12:12" ht="21" customHeight="1">
       <c r="L21" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="22" spans="12:12" ht="21" customHeight="1">
@@ -9539,7 +9568,7 @@
         <v>9</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="I2" s="1" t="s">
         <v>15</v>
@@ -9551,7 +9580,7 @@
         <v>3</v>
       </c>
       <c r="R2" s="4" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
     </row>
     <row r="3" spans="1:18" ht="21" customHeight="1">
@@ -9559,13 +9588,13 @@
         <v>12</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H3" s="1" t="s">
         <v>12</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="J3" s="1" t="s">
         <v>17</v>
@@ -9580,7 +9609,7 @@
         <v>5</v>
       </c>
       <c r="R3" s="4" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
     </row>
     <row r="4" spans="1:18" ht="21" customHeight="1">
@@ -9591,13 +9620,13 @@
         <v>13</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="Q4" s="3">
         <v>6</v>
       </c>
       <c r="R4" s="4" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
     </row>
     <row r="5" spans="1:18" ht="21" customHeight="1">
@@ -9614,7 +9643,7 @@
         <v>8</v>
       </c>
       <c r="R5" s="4" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
     </row>
     <row r="6" spans="1:18" ht="21" customHeight="1">
@@ -9652,7 +9681,7 @@
         <v>9</v>
       </c>
       <c r="R6" s="4" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
     </row>
     <row r="7" spans="1:18" ht="21" customHeight="1">
@@ -9660,7 +9689,7 @@
         <v>2</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="8" spans="1:18" ht="21" customHeight="1">
@@ -9673,13 +9702,13 @@
     </row>
     <row r="9" spans="1:18" ht="21" customHeight="1">
       <c r="E9" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H9" s="1" t="s">
         <v>13</v>
       </c>
       <c r="Q9" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="10" spans="1:18" ht="21" customHeight="1">
@@ -9693,7 +9722,7 @@
         <v>9</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H10" s="1" t="s">
         <v>8</v>
@@ -9708,12 +9737,12 @@
         <v>1</v>
       </c>
       <c r="R10" s="4" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
     </row>
     <row r="11" spans="1:18" ht="21" customHeight="1">
       <c r="E11" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="H11" s="1" t="s">
         <v>9</v>
@@ -9722,7 +9751,7 @@
         <v>2</v>
       </c>
       <c r="R11" s="4" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
     </row>
     <row r="12" spans="1:18" ht="21" customHeight="1">
@@ -9733,12 +9762,12 @@
         <v>4</v>
       </c>
       <c r="R12" s="4" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
     </row>
     <row r="13" spans="1:18" ht="21" customHeight="1">
       <c r="A13" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>12</v>
@@ -9747,7 +9776,7 @@
         <v>0</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>9</v>
@@ -9765,7 +9794,7 @@
         <v>7</v>
       </c>
       <c r="R13" s="4" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
     </row>
     <row r="14" spans="1:18" ht="21" customHeight="1">
@@ -9779,7 +9808,7 @@
         <v>9</v>
       </c>
       <c r="R14" s="4" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
     </row>
     <row r="15" spans="1:18" ht="21" customHeight="1">
@@ -9799,7 +9828,7 @@
     </row>
     <row r="18" spans="1:1" ht="21" customHeight="1">
       <c r="A18" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="19" spans="1:1" ht="21" customHeight="1">
@@ -9851,10 +9880,10 @@
         <v>4</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>8</v>
@@ -9869,7 +9898,7 @@
         <v>4</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Q1" s="2" t="s">
         <v>7</v>
@@ -9880,27 +9909,27 @@
         <v>9</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="Q2" s="3">
         <v>1</v>
       </c>
       <c r="R2" s="4" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
     </row>
     <row r="3" spans="1:18" ht="21" customHeight="1">
       <c r="A3" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>15</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>9</v>
@@ -9909,10 +9938,10 @@
         <v>8</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I3" s="1" t="s">
         <v>12</v>
@@ -9921,7 +9950,7 @@
         <v>4</v>
       </c>
       <c r="R3" s="4" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
     </row>
     <row r="4" spans="1:18" ht="21" customHeight="1">
@@ -9938,7 +9967,7 @@
         <v>7</v>
       </c>
       <c r="R4" s="4" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
     </row>
     <row r="5" spans="1:18" ht="21" customHeight="1">
@@ -9955,12 +9984,12 @@
         <v>9</v>
       </c>
       <c r="R5" s="4" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
     </row>
     <row r="6" spans="1:18" ht="21" customHeight="1">
       <c r="A6" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>8</v>
@@ -9972,7 +10001,7 @@
         <v>10</v>
       </c>
       <c r="R6" s="4" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
     </row>
     <row r="7" spans="1:18" ht="21" customHeight="1">
@@ -9980,7 +10009,7 @@
         <v>2</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I7" s="1" t="s">
         <v>11</v>
@@ -9988,7 +10017,7 @@
     </row>
     <row r="8" spans="1:18" ht="21" customHeight="1">
       <c r="F8" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I8" s="1" t="s">
         <v>4</v>
@@ -9999,7 +10028,7 @@
         <v>12</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>8</v>
@@ -10026,12 +10055,12 @@
         <v>12</v>
       </c>
       <c r="Q9" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="10" spans="1:18" ht="21" customHeight="1">
       <c r="F10" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="I10" s="1" t="s">
         <v>8</v>
@@ -10040,7 +10069,7 @@
         <v>2</v>
       </c>
       <c r="R10" s="4" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
     </row>
     <row r="11" spans="1:18" ht="21" customHeight="1">
@@ -10051,7 +10080,7 @@
         <v>3</v>
       </c>
       <c r="R11" s="4" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
     </row>
     <row r="12" spans="1:18" ht="21" customHeight="1">
@@ -10065,12 +10094,12 @@
         <v>5</v>
       </c>
       <c r="R12" s="4" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
     </row>
     <row r="13" spans="1:18" ht="21" customHeight="1">
       <c r="D13" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>12</v>
@@ -10097,7 +10126,7 @@
         <v>6</v>
       </c>
       <c r="R13" s="4" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
     </row>
     <row r="14" spans="1:18" ht="21" customHeight="1">
@@ -10111,7 +10140,7 @@
         <v>8</v>
       </c>
       <c r="R14" s="4" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
     </row>
     <row r="15" spans="1:18" ht="21" customHeight="1">
@@ -10121,7 +10150,7 @@
     </row>
     <row r="16" spans="1:18" ht="21" customHeight="1">
       <c r="A16" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>12</v>
@@ -10198,13 +10227,13 @@
         <v>15</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>5</v>
@@ -10227,7 +10256,7 @@
         <v>1</v>
       </c>
       <c r="R2" s="4" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
     </row>
     <row r="3" spans="1:18" ht="21" customHeight="1">
@@ -10241,7 +10270,7 @@
         <v>5</v>
       </c>
       <c r="R3" s="4" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
     </row>
     <row r="4" spans="1:18" ht="21" customHeight="1">
@@ -10258,7 +10287,7 @@
         <v>7</v>
       </c>
       <c r="R4" s="4" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
     </row>
     <row r="5" spans="1:18" ht="21" customHeight="1">
@@ -10266,7 +10295,7 @@
         <v>12</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J5" s="1" t="s">
         <v>0</v>
@@ -10275,7 +10304,7 @@
         <v>8</v>
       </c>
       <c r="R5" s="4" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
     </row>
     <row r="6" spans="1:18" ht="21" customHeight="1">
@@ -10304,7 +10333,7 @@
         <v>9</v>
       </c>
       <c r="R6" s="4" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
     </row>
     <row r="7" spans="1:18" ht="21" customHeight="1">
@@ -10323,7 +10352,7 @@
         <v>2</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H8" s="1" t="s">
         <v>5</v>
@@ -10340,12 +10369,12 @@
         <v>5</v>
       </c>
       <c r="Q9" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="10" spans="1:18" ht="21" customHeight="1">
       <c r="A10" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>8</v>
@@ -10372,7 +10401,7 @@
         <v>2</v>
       </c>
       <c r="R10" s="4" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
     </row>
     <row r="11" spans="1:18" ht="21" customHeight="1">
@@ -10386,12 +10415,12 @@
         <v>3</v>
       </c>
       <c r="R11" s="4" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
     </row>
     <row r="12" spans="1:18" ht="21" customHeight="1">
       <c r="A12" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>9</v>
@@ -10400,7 +10429,7 @@
         <v>4</v>
       </c>
       <c r="R12" s="4" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
     </row>
     <row r="13" spans="1:18" ht="21" customHeight="1">
@@ -10414,7 +10443,7 @@
         <v>6</v>
       </c>
       <c r="R13" s="4" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
     </row>
     <row r="14" spans="1:18" ht="21" customHeight="1">
@@ -10425,10 +10454,10 @@
         <v>8</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F14" s="1" t="s">
         <v>9</v>
@@ -10446,12 +10475,12 @@
         <v>7</v>
       </c>
       <c r="R14" s="4" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
     </row>
     <row r="15" spans="1:18" ht="21" customHeight="1">
       <c r="A15" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>5</v>
@@ -10469,7 +10498,7 @@
     </row>
     <row r="18" spans="1:9" ht="21" customHeight="1">
       <c r="A18" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>12</v>
@@ -10481,7 +10510,7 @@
         <v>14</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F18" s="1" t="s">
         <v>3</v>
@@ -10498,7 +10527,7 @@
     </row>
     <row r="19" spans="1:9" ht="21" customHeight="1">
       <c r="A19" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="20" spans="1:9" ht="21" customHeight="1">
@@ -10538,7 +10567,7 @@
   <sheetData>
     <row r="1" spans="1:18" ht="21" customHeight="1">
       <c r="D1" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="Q1" s="2" t="s">
         <v>7</v>
@@ -10570,7 +10599,7 @@
         <v>2</v>
       </c>
       <c r="R2" s="4" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
     </row>
     <row r="3" spans="1:18" ht="21" customHeight="1">
@@ -10578,13 +10607,13 @@
         <v>13</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="Q3" s="3">
         <v>5</v>
       </c>
       <c r="R3" s="4" t="s">
-        <v>105</v>
+        <v>220</v>
       </c>
     </row>
     <row r="4" spans="1:18" ht="21" customHeight="1">
@@ -10592,18 +10621,18 @@
         <v>14</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Q4" s="3">
         <v>6</v>
       </c>
       <c r="R4" s="4" t="s">
-        <v>106</v>
+        <v>97</v>
       </c>
     </row>
     <row r="5" spans="1:18" ht="21" customHeight="1">
       <c r="D5" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G5" s="1" t="s">
         <v>15</v>
@@ -10612,7 +10641,7 @@
         <v>8</v>
       </c>
       <c r="R5" s="4" t="s">
-        <v>107</v>
+        <v>98</v>
       </c>
     </row>
     <row r="6" spans="1:18" ht="21" customHeight="1">
@@ -10626,12 +10655,12 @@
         <v>9</v>
       </c>
       <c r="R6" s="4" t="s">
-        <v>108</v>
+        <v>99</v>
       </c>
     </row>
     <row r="7" spans="1:18" ht="21" customHeight="1">
       <c r="E7" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="G7" s="1" t="s">
         <v>20</v>
@@ -10662,7 +10691,7 @@
         <v>0</v>
       </c>
       <c r="Q9" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="10" spans="1:18" ht="21" customHeight="1">
@@ -10697,7 +10726,7 @@
         <v>1</v>
       </c>
       <c r="R10" s="4" t="s">
-        <v>109</v>
+        <v>100</v>
       </c>
     </row>
     <row r="11" spans="1:18" ht="21" customHeight="1">
@@ -10708,7 +10737,7 @@
         <v>3</v>
       </c>
       <c r="R11" s="4" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
     </row>
     <row r="12" spans="1:18" ht="21" customHeight="1">
@@ -10716,13 +10745,13 @@
         <v>17</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="Q12" s="3">
         <v>4</v>
       </c>
       <c r="R12" s="4" t="s">
-        <v>111</v>
+        <v>221</v>
       </c>
     </row>
     <row r="13" spans="1:18" ht="21" customHeight="1">
@@ -10730,7 +10759,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>11</v>
@@ -10748,10 +10777,10 @@
         <v>12</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J13" s="1" t="s">
         <v>12</v>
@@ -10760,7 +10789,7 @@
         <v>7</v>
       </c>
       <c r="R13" s="4" t="s">
-        <v>112</v>
+        <v>102</v>
       </c>
     </row>
     <row r="14" spans="1:18" ht="21" customHeight="1">
@@ -10777,7 +10806,7 @@
         <v>8</v>
       </c>
       <c r="R14" s="4" t="s">
-        <v>113</v>
+        <v>103</v>
       </c>
     </row>
     <row r="15" spans="1:18" ht="21" customHeight="1">
@@ -10803,7 +10832,7 @@
         <v>17</v>
       </c>
       <c r="M15" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="16" spans="1:18" ht="21" customHeight="1">
@@ -10840,7 +10869,7 @@
     </row>
     <row r="20" spans="1:10" ht="21" customHeight="1">
       <c r="A20" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="21" spans="1:10" ht="21" customHeight="1">

--- a/src/vocabulary_crossword_puzzles_20tabs.xlsx
+++ b/src/vocabulary_crossword_puzzles_20tabs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kachowyau/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7570F0B7-539B-EA45-A7B3-C5BB2FEE36B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61B3752C-2B99-B844-ADA8-262E9D3654AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15940" firstSheet="7" activeTab="19" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="14320" windowHeight="15940" firstSheet="14" activeTab="19" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Puzzle_01" sheetId="1" r:id="rId1"/>
@@ -213,67 +213,67 @@
         <r>
           <rPr>
             <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="新細明體"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>2</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="G1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0900-000003000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="新細明體"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>3</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="N1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0900-000004000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="新細明體"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>4</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="A3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0900-000005000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="新細明體"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>5</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="B3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0900-000006000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
             <color rgb="FF000000"/>
             <rFont val="新細明體"/>
             <family val="1"/>
             <charset val="136"/>
           </rPr>
+          <t>2</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0900-000003000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="新細明體"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>3</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="N1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0900-000004000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="新細明體"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>4</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="A3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0900-000005000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="新細明體"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>5</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="B3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0900-000006000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color rgb="FF000000"/>
+            <rFont val="新細明體"/>
+            <family val="1"/>
+            <charset val="136"/>
+          </rPr>
           <t>6</t>
         </r>
       </text>
@@ -297,10 +297,10 @@
         <r>
           <rPr>
             <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="新細明體"/>
-            <family val="2"/>
-            <scheme val="minor"/>
+            <color rgb="FF000000"/>
+            <rFont val="新細明體"/>
+            <family val="1"/>
+            <charset val="136"/>
           </rPr>
           <t>8</t>
         </r>
@@ -1943,10 +1943,10 @@
         <r>
           <rPr>
             <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="新細明體"/>
-            <family val="2"/>
-            <scheme val="minor"/>
+            <color rgb="FF000000"/>
+            <rFont val="新細明體"/>
+            <family val="1"/>
+            <charset val="136"/>
           </rPr>
           <t>2</t>
         </r>
@@ -2257,10 +2257,10 @@
         <r>
           <rPr>
             <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="新細明體"/>
-            <family val="2"/>
-            <scheme val="minor"/>
+            <color rgb="FF000000"/>
+            <rFont val="新細明體"/>
+            <family val="1"/>
+            <charset val="136"/>
           </rPr>
           <t>3</t>
         </r>
@@ -2313,10 +2313,10 @@
         <r>
           <rPr>
             <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="新細明體"/>
-            <family val="2"/>
-            <scheme val="minor"/>
+            <color rgb="FF000000"/>
+            <rFont val="新細明體"/>
+            <family val="1"/>
+            <charset val="136"/>
           </rPr>
           <t>7</t>
         </r>
@@ -3607,10 +3607,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>(adj.) vvery large in amount or degree</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>(adj.) determined to win or succeed and using forceful action to do this</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -3624,6 +3620,10 @@
   </si>
   <si>
     <t>(n./v.) to give up something that is valuable to you in order to help another person</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>(adj.) very large in amount or degree</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -4571,7 +4571,7 @@
         <v>2</v>
       </c>
       <c r="R10" s="4" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
     </row>
     <row r="11" spans="1:18" ht="21" customHeight="1">
@@ -4628,7 +4628,7 @@
         <v>6</v>
       </c>
       <c r="R13" s="4" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="14" spans="1:18" ht="21" customHeight="1">
@@ -4894,7 +4894,7 @@
         <v>4</v>
       </c>
       <c r="R12" s="4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="13" spans="1:18" ht="21" customHeight="1">
@@ -5082,7 +5082,7 @@
         <v>3</v>
       </c>
       <c r="R3" s="4" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="4" spans="1:18" ht="21" customHeight="1">
@@ -7355,7 +7355,7 @@
         <v>6</v>
       </c>
       <c r="R13" s="4" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="14" spans="1:18" ht="21" customHeight="1">
